--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512638_ELIMINGRB14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512638_ELIMINGRB14FINAL_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3289</v>
+        <v>2.3546</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3678</v>
+        <v>1.9108</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9611</v>
+        <v>0.4437</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6954</v>
+        <v>-0.1994</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4293</v>
+        <v>-0.0939</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1248</v>
+        <v>-0.1055</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9253</v>
+        <v>0.1637</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3145</v>
+        <v>0.1232</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2398</v>
+        <v>0.0405</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2299</v>
+        <v>-0.3631</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1149</v>
+        <v>-0.2171</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.115</v>
+        <v>-0.146</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6005</v>
+        <v>0.9737</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6005</v>
+        <v>0.9737</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6329</v>
+        <v>0.3593</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7826</v>
+        <v>0.5261</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1497</v>
+        <v>-0.1668</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5999</v>
+        <v>1.2211</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3401</v>
+        <v>1.2211</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GARCIA QUILEZ CUERVAS</t>
+          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1618</v>
+        <v>2.1042</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7866</v>
+        <v>1.2794</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3753</v>
+        <v>0.8248</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.155</v>
+        <v>0.7071</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0731</v>
+        <v>-0.3966</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0819</v>
+        <v>1.1037</v>
       </c>
       <c r="J3" t="n">
-        <v>0.16</v>
+        <v>1.0281</v>
       </c>
       <c r="K3" t="n">
-        <v>0.12</v>
+        <v>-0.2283</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04</v>
+        <v>1.2563</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3149</v>
+        <v>-0.321</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.193</v>
+        <v>-0.1684</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1219</v>
+        <v>-0.1526</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0003</v>
+        <v>1.5579</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0003</v>
+        <v>1.5579</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1167</v>
+        <v>0.4497</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4269</v>
+        <v>0.5824</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3101</v>
+        <v>-0.1327</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1998</v>
+        <v>-0.6105</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1998</v>
+        <v>-0.3311</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. VILA DE MIGUEL</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9159</v>
+        <v>1.9357</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6158</v>
+        <v>1.568</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3001</v>
+        <v>0.3677</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2094</v>
+        <v>-0.0069</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2025</v>
+        <v>1.734</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0069</v>
+        <v>-1.7408</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06</v>
+        <v>-0.6464</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06</v>
+        <v>1.3471</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-1.9935</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1494</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1425</v>
+        <v>0.3869</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0069</v>
+        <v>0.2527</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4001</v>
+        <v>0.9737</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6262</v>
+        <v>0.0789</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5558</v>
+        <v>0.1034</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0704</v>
+        <v>-0.0245</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6802</v>
+        <v>0.89</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.1111</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6802</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>O. MENDEZ BLANCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5081</v>
+        <v>1.9036</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7268</v>
+        <v>0.0953</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7813</v>
+        <v>1.8083</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0539</v>
+        <v>-0.3216</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6952</v>
+        <v>2.5021</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.7491</v>
+        <v>-2.8237</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7526</v>
+        <v>-0.3257</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2814</v>
+        <v>1.6678</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.034</v>
+        <v>-1.9935</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6986</v>
+        <v>0.0041</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4137</v>
+        <v>0.8343</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2849</v>
+        <v>-0.8302</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0003</v>
+        <v>0.3895</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0003</v>
+        <v>2.3368</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2979</v>
+        <v>-0.3269</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.0738</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2822</v>
+        <v>-0.2531</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8597</v>
+        <v>2.1626</v>
       </c>
       <c r="W5" t="n">
-        <v>2.0594</v>
+        <v>2.4421</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1998</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>C. VILA DE MIGUEL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4184</v>
+        <v>1.5685</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5019</v>
+        <v>0.3126</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9203</v>
+        <v>1.2558</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9162</v>
+        <v>0.1761</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.601</v>
+        <v>0.1827</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6849</v>
+        <v>-0.0066</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.3503</v>
+        <v>0.0616</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.3503</v>
+        <v>0.0616</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4341</v>
+        <v>0.1145</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7493</v>
+        <v>0.1211</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6849</v>
+        <v>-0.0066</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6002</v>
+        <v>0.3895</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4004</v>
+        <v>0.3895</v>
       </c>
       <c r="S6" t="n">
-        <v>0.795</v>
+        <v>0.3408</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3894</v>
+        <v>0.251</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5944</v>
+        <v>0.0897</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1398</v>
+        <v>0.6621</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. MENDEZ BLANCO</t>
+          <t>A. PEREZ CONTI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8331</v>
+        <v>1.3392</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2187</v>
+        <v>0.1692</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0518</v>
+        <v>1.17</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3515</v>
+        <v>1.1908</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4619</v>
+        <v>-0.3653</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.8133</v>
+        <v>1.5561</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4708</v>
+        <v>0.9143</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5632</v>
+        <v>-0.9338</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.034</v>
+        <v>1.8481</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1194</v>
+        <v>0.2765</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.5685</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7793</v>
+        <v>-0.292</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4001</v>
+        <v>0.7789</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0006</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4007</v>
+        <v>1.7526</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3553</v>
+        <v>0.0316</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1468</v>
+        <v>-0.3304</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2084</v>
+        <v>0.362</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1398</v>
+        <v>-0.6621</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3995</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2598</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PEREZ CONTI</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3435</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1229</v>
+        <v>-2.1621</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4664</v>
+        <v>3.0437</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1529</v>
+        <v>-0.8722</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.405</v>
+        <v>-1.5301</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5579</v>
+        <v>0.6579</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7692</v>
+        <v>-2.2552</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0325</v>
+        <v>-2.2552</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8016</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3837</v>
+        <v>1.383</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.725</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2438</v>
+        <v>0.6579</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-1.9474</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8005</v>
+        <v>1.3632</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9294</v>
+        <v>0.1754</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4114</v>
+        <v>0.5399</v>
       </c>
       <c r="U8" t="n">
-        <v>0.482</v>
+        <v>-0.3646</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6802</v>
+        <v>2.1626</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5196</v>
+        <v>1.5005</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1998</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ROLDAN DE LA PORTILLA</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4519</v>
+        <v>-0.7348</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9436</v>
+        <v>-1.2434</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4917</v>
+        <v>0.5085</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8982</v>
+        <v>-2.0477</v>
       </c>
       <c r="H9" t="n">
-        <v>1.882</v>
+        <v>2.7356</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.7802</v>
+        <v>-4.7833</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7326</v>
+        <v>-0.9702</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2614</v>
+        <v>2.3118</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.994</v>
+        <v>-3.282</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1656</v>
+        <v>-1.0775</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6206</v>
+        <v>0.4238</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7862</v>
+        <v>-1.5013</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6002</v>
+        <v>1.7526</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6005</v>
+        <v>1.7526</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0459</v>
+        <v>-0.4398</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7893</v>
+        <v>-0.2732</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2566</v>
+        <v>-0.1666</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>A. ROLDAN DE LA PORTILLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0974</v>
+        <v>-1.1211</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5978</v>
+        <v>-1.3075</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6952</v>
+        <v>0.1865</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5841</v>
+        <v>-0.8698</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7423</v>
+        <v>1.9069</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8418</v>
+        <v>-2.7766</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2763</v>
+        <v>-0.6264</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3563</v>
+        <v>1.3266</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08</v>
+        <v>-1.953</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3078</v>
+        <v>-0.2433</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3861</v>
+        <v>0.5803</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9218</v>
+        <v>-0.8236</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4001</v>
+        <v>1.5579</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8862</v>
+        <v>0.3856</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8741</v>
+        <v>0.2926</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0122</v>
+        <v>0.093</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7997</v>
+        <v>-1.2211</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7997</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4545</v>
+        <v>-2.1922</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2112</v>
+        <v>0.4983</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7567</v>
+        <v>-2.6905</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0805</v>
+        <v>-1.6124</v>
       </c>
       <c r="H11" t="n">
-        <v>2.72</v>
+        <v>-0.7369</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.8005</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1288</v>
+        <v>-0.2216</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2212</v>
+        <v>-0.3027</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.35</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9517</v>
+        <v>-1.3907</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4988</v>
+        <v>-0.4342</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4505</v>
+        <v>-0.9565</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8005</v>
+        <v>0.3895</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8005</v>
+        <v>0.3895</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1746</v>
+        <v>0.8622</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0824</v>
+        <v>0.7199</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0922</v>
+        <v>0.1424</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.8316</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1877</v>
+        <v>-2.9094</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9487</v>
+        <v>-2.4319</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.239</v>
+        <v>-0.4775</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9096</v>
+        <v>-2.8648</v>
       </c>
       <c r="H12" t="n">
-        <v>0.453</v>
+        <v>0.4839</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.3626</v>
+        <v>-3.3488</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.0865</v>
+        <v>-2.9479</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3745</v>
+        <v>-0.2898</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.712</v>
+        <v>-2.658</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1769</v>
+        <v>0.083</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8274</v>
+        <v>0.7738</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6506</v>
+        <v>-0.6907</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7816</v>
+        <v>0.0401</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9382</v>
+        <v>0.2686</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1566</v>
+        <v>-0.2284</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.364</v>
+        <v>-3.414</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9593</v>
+        <v>-2.9228</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4046</v>
+        <v>-0.4911</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2116</v>
+        <v>-2.1809</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2342</v>
+        <v>-1.1725</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9774</v>
+        <v>-1.0084</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.9886</v>
+        <v>-1.8533</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3906</v>
+        <v>-1.2699</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.223</v>
+        <v>-0.3275</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1563</v>
+        <v>0.0974</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3794</v>
+        <v>-0.4249</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.6007</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6711</v>
+        <v>0.129</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2889</v>
+        <v>0.4347</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3822</v>
+        <v>-0.3057</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1195</v>
+        <v>1.1695</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3192</v>
+        <v>2.3905</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.954200000000001</v>
+        <v>1.715899999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.811500000000001</v>
+        <v>-4.2341</v>
       </c>
       <c r="F14" t="n">
-        <v>7.765899999999998</v>
+        <v>5.9499</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.1029</v>
+        <v>-8.9017</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9297</v>
+        <v>5.2499</v>
       </c>
       <c r="I14" t="n">
-        <v>-14.0323</v>
+        <v>-14.1515</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.872</v>
+        <v>-7.678999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6885000000000003</v>
+        <v>1.5584</v>
       </c>
       <c r="L14" t="n">
-        <v>-9.560600000000001</v>
+        <v>-9.237500000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2308000000000003</v>
+        <v>-1.2224</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2408</v>
+        <v>3.6914</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.4718</v>
+        <v>-4.9138</v>
       </c>
       <c r="P14" t="n">
-        <v>5.001499999999999</v>
+        <v>4.8684</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.0032</v>
+        <v>-10.7106</v>
       </c>
       <c r="R14" t="n">
-        <v>16.0046</v>
+        <v>15.579</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4562</v>
+        <v>2.0859</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2467</v>
+        <v>3.0412</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7902000000000001</v>
+        <v>-0.9553</v>
       </c>
       <c r="V14" t="n">
-        <v>3.599400000000001</v>
+        <v>3.663099999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>10.8168</v>
+        <v>11.1143</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.217699999999999</v>
+        <v>-7.4513</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.7567</v>
+        <v>8.0131</v>
       </c>
       <c r="E15" t="n">
-        <v>7.2824</v>
+        <v>7.3893</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4743</v>
+        <v>0.6237</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2205</v>
+        <v>3.1851</v>
       </c>
       <c r="H15" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.1238</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2121</v>
+        <v>3.3089</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0872</v>
+        <v>3.2204</v>
       </c>
       <c r="K15" t="n">
-        <v>0.16</v>
+        <v>0.1642</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9272</v>
+        <v>3.0562</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1334</v>
+        <v>-0.0353</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1515</v>
+        <v>-0.288</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2849</v>
+        <v>0.2527</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4839</v>
+        <v>-0.1862</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5959</v>
+        <v>0.5058</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0798</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>3.2196</v>
+        <v>3.2616</v>
       </c>
       <c r="W15" t="n">
-        <v>3.5993</v>
+        <v>3.6632</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3798</v>
+        <v>-0.4016</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0872</v>
+        <v>2.7166</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2561</v>
+        <v>2.0528</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5983</v>
+        <v>2.5743</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5603</v>
+        <v>1.5451</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0379</v>
+        <v>1.0292</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6653</v>
+        <v>0.7675</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2614</v>
+        <v>1.3266</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5961</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9329</v>
+        <v>1.8068</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2989</v>
+        <v>0.2185</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6341</v>
+        <v>1.5883</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9096</v>
+        <v>0.5039</v>
       </c>
       <c r="T16" t="n">
-        <v>0.467</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4426</v>
+        <v>0.4208</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6207</v>
+        <v>-0.5563</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.7869</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3197</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4662</v>
+        <v>0.6696</v>
       </c>
       <c r="E17" t="n">
-        <v>0.21</v>
+        <v>0.6273</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2562</v>
+        <v>0.0423</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0343</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1094</v>
+        <v>0.0682</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9248</v>
+        <v>0.9011</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8434</v>
+        <v>0.9257</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6034</v>
+        <v>0.6826</v>
       </c>
       <c r="L17" t="n">
-        <v>0.24</v>
+        <v>0.2432</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1909</v>
+        <v>0.0436</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.494</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6849</v>
+        <v>0.6579</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3686</v>
+        <v>-0.0471</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0468</v>
+        <v>0.3636</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4154</v>
+        <v>-0.4107</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.9999</v>
+        <v>-2.0053</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3197</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="18">
@@ -1813,28 +1813,28 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. CONDES LOPEZ-CEPERO</t>
+          <t>G. ZALAZAR RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4498</v>
+        <v>-0.6083</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7354000000000001</v>
+        <v>-2.4321</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1852</v>
+        <v>1.8238</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7181</v>
+        <v>0.9534</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5042</v>
+        <v>-1.5753</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2223</v>
+        <v>2.5287</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6491</v>
+        <v>-0.6297</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1527</v>
+        <v>-1.9755</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8018</v>
+        <v>1.3457</v>
       </c>
       <c r="M19" t="n">
-        <v>0.06900000000000001</v>
+        <v>1.5831</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3515</v>
+        <v>0.4001</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4205</v>
+        <v>1.183</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.2003</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8005</v>
+        <v>0.9737</v>
       </c>
       <c r="S19" t="n">
-        <v>0.672</v>
+        <v>-0.1544</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8874</v>
+        <v>-0.1024</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2154</v>
+        <v>-0.0519</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6395999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8393</v>
+        <v>-0.6811</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. ZALAZAR RODRIGUEZ</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7141</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.166</v>
+        <v>-3.1708</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4519</v>
+        <v>2.3869</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9218</v>
+        <v>0.2187</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5959</v>
+        <v>-1.5513</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5177</v>
+        <v>1.77</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8249</v>
+        <v>-1.2262</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.1086</v>
+        <v>-1.2751</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2836</v>
+        <v>0.0489</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7467</v>
+        <v>1.4449</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5125999999999999</v>
+        <v>-0.2762</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2341</v>
+        <v>1.7212</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0006</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0003</v>
+        <v>1.3632</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1955</v>
+        <v>-0.3862</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.54</v>
+        <v>-0.2446</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3445</v>
+        <v>-0.1417</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5602</v>
+        <v>0.9416</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>I. CONDES LOPEZ-CEPERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-1.0686</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.407</v>
+        <v>-0.1195</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4457</v>
+        <v>-0.9492</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2808</v>
+        <v>0.6966</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4927</v>
+        <v>-0.5239</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7735</v>
+        <v>1.2206</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3304</v>
+        <v>0.8043</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3342</v>
+        <v>-0.0306</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0038</v>
+        <v>0.835</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6112</v>
+        <v>-0.1077</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1585</v>
+        <v>-0.4933</v>
       </c>
       <c r="O21" t="n">
-        <v>1.7697</v>
+        <v>0.3856</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6005</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4004</v>
+        <v>1.7526</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5816</v>
+        <v>0.0842</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2755</v>
+        <v>0.7762</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3061</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.6811</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2598</v>
+        <v>-1.9021</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7822</v>
+        <v>-1.2643</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5321</v>
+        <v>-2.2298</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7499</v>
+        <v>0.9655</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6829</v>
+        <v>1.6367</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6242</v>
+        <v>-0.6471</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3071</v>
+        <v>2.2838</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0419</v>
+        <v>0.0655</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.638</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6889</v>
       </c>
       <c r="M22" t="n">
-        <v>1.641</v>
+        <v>1.5712</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0138</v>
+        <v>-0.0236</v>
       </c>
       <c r="O22" t="n">
-        <v>1.6272</v>
+        <v>1.5948</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6649</v>
+        <v>-0.1221</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5734</v>
+        <v>-0.3479</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0914</v>
+        <v>0.2259</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9387</v>
+        <v>-1.6766</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4949</v>
+        <v>-2.0578</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5562</v>
+        <v>0.3812</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7913</v>
+        <v>0.78</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2817</v>
+        <v>-0.3208</v>
       </c>
       <c r="I23" t="n">
-        <v>1.073</v>
+        <v>1.1008</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7923</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.638</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1543</v>
+        <v>-0.0888</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5835</v>
+        <v>1.4922</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3563</v>
+        <v>0.3027</v>
       </c>
       <c r="O23" t="n">
-        <v>1.2273</v>
+        <v>1.1896</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3302</v>
+        <v>-0.0408</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7023</v>
+        <v>-0.3719</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3722</v>
+        <v>0.3311</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.7182</v>
+        <v>-6.0739</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.5247</v>
+        <v>-4.9283</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1935</v>
+        <v>-1.1456</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.445</v>
+        <v>-2.4204</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.4088</v>
+        <v>-2.4287</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0362</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.4083</v>
+        <v>-2.3007</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.6941</v>
+        <v>-1.6446</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.6561</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0367</v>
+        <v>-0.1197</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7147</v>
+        <v>-0.7842</v>
       </c>
       <c r="O24" t="n">
-        <v>0.678</v>
+        <v>0.6645</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8005</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4132</v>
+        <v>0.2102</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1155</v>
+        <v>0.2935</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2977</v>
+        <v>-0.0833</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.0594</v>
+        <v>-2.1111</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.0594</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.9541999999999993</v>
+        <v>0.2317</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.7659</v>
+        <v>-5.949999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>6.8116</v>
+        <v>6.1814</v>
       </c>
       <c r="G25" t="n">
-        <v>9.102899999999998</v>
+        <v>8.901599999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>-4.929500000000001</v>
+        <v>-5.2497</v>
       </c>
       <c r="I25" t="n">
-        <v>14.0322</v>
+        <v>14.1515</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2309000000000005</v>
+        <v>1.2225</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.240899999999999</v>
+        <v>-3.6915</v>
       </c>
       <c r="L25" t="n">
-        <v>4.4717</v>
+        <v>4.913999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>8.8719</v>
+        <v>7.6791</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6886000000000001</v>
+        <v>-1.5584</v>
       </c>
       <c r="O25" t="n">
-        <v>9.560700000000001</v>
+        <v>9.2376</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.0015</v>
+        <v>-4.8685</v>
       </c>
       <c r="Q25" t="n">
-        <v>-16.0048</v>
+        <v>-15.5788</v>
       </c>
       <c r="R25" t="n">
-        <v>11.003</v>
+        <v>10.7105</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4563</v>
+        <v>-0.1385000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7903999999999998</v>
+        <v>0.9553999999999998</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.2465</v>
+        <v>-1.0938</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.5993</v>
+        <v>-3.6633</v>
       </c>
       <c r="W25" t="n">
-        <v>7.2176</v>
+        <v>7.4513</v>
       </c>
       <c r="X25" t="n">
-        <v>-10.8168</v>
+        <v>-11.1145</v>
       </c>
     </row>
   </sheetData>
